--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2007-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2007-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB25C83D-3566-4FF8-86DF-48D9FDD9228A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDEED9C5-C4B6-47E8-B79E-52DC31A9D05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{97BEA5F7-70DA-4EB6-8015-6E532885A30C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F474E205-9A7A-4301-AF08-3235138C2BC5}"/>
   </bookViews>
   <sheets>
     <sheet name="2007-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1415,24 +1415,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D76234F9-7A2E-4645-AE47-85154F04A774}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA674500-D39F-44F3-9AF3-00842816FF63}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="14" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1466,7 +1465,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1502,7 +1501,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1554,7 +1553,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1622,7 +1621,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1694,7 +1693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1766,7 +1765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1838,7 +1837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1910,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -1982,7 +1981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2054,7 +2053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2126,7 +2125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2198,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2342,7 +2341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2414,7 +2413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2486,7 +2485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2558,7 +2557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2630,7 +2629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2702,7 +2701,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2774,7 +2773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2846,7 +2845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2918,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -2990,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2005</v>
       </c>
@@ -3062,7 +3061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2004</v>
       </c>
@@ -3134,7 +3133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2003</v>
       </c>
@@ -3206,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2002</v>
       </c>
@@ -3278,7 +3277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3350,7 +3349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>2000</v>
       </c>
@@ -3422,7 +3421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>1999</v>
       </c>
@@ -3494,7 +3493,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>1998</v>
       </c>
@@ -3566,7 +3565,7 @@
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>1997</v>
       </c>
@@ -3638,7 +3637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>1996</v>
       </c>
@@ -3710,7 +3709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>1995</v>
       </c>
@@ -3782,7 +3781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>1994</v>
       </c>
@@ -3854,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>1993</v>
       </c>
@@ -3926,7 +3925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>1992</v>
       </c>
@@ -3998,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>1991</v>
       </c>
@@ -4070,7 +4069,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="33">
         <v>1990</v>
       </c>
@@ -4142,7 +4141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>1989</v>
       </c>
@@ -4214,7 +4213,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="33">
         <v>1988</v>
       </c>
@@ -4286,7 +4285,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35" t="s">
         <v>31</v>
       </c>
